--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП СПОРТ-ВАРНА/ОП СПОРТ-ВАРНА.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП СПОРТ-ВАРНА/ОП СПОРТ-ВАРНА.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="26">
   <si>
     <t>Дата</t>
   </si>
@@ -53,9 +53,6 @@
   </si>
   <si>
     <t>Billing_Document</t>
-  </si>
-  <si>
-    <t>2026-05-11</t>
   </si>
   <si>
     <t>ТубаСпорт1</t>
@@ -101,8 +98,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="#,##0.00"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -188,11 +186,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -200,9 +199,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -556,20 +555,20 @@
       </c>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2" t="s">
-        <v>13</v>
+      <c r="A2" s="2">
+        <v>46153</v>
       </c>
       <c r="B2">
         <v>1146</v>
       </c>
       <c r="C2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" t="s">
         <v>14</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>15</v>
-      </c>
-      <c r="E2" t="s">
-        <v>16</v>
       </c>
       <c r="F2">
         <v>40</v>
@@ -587,7 +586,7 @@
         <v>61.6</v>
       </c>
       <c r="K2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -597,80 +596,80 @@
       </c>
     </row>
     <row r="5" spans="1:13">
-      <c r="A5" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
+      <c r="A5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
     </row>
     <row r="6" spans="1:13">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="D6" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="E6" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="F6" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="G6" s="4" t="s">
         <v>24</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:13">
-      <c r="A7" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" s="5">
+      <c r="A7" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="6">
         <v>40</v>
       </c>
-      <c r="C7" s="5">
+      <c r="C7" s="6">
         <v>1</v>
       </c>
-      <c r="D7" s="5">
+      <c r="D7" s="6">
         <v>1.51</v>
       </c>
-      <c r="E7" s="5">
+      <c r="E7" s="6">
         <v>60.4</v>
       </c>
-      <c r="F7" s="5">
+      <c r="F7" s="6">
         <v>61.6</v>
       </c>
-      <c r="G7" s="5">
+      <c r="G7" s="6">
         <v>1.2</v>
       </c>
     </row>
     <row r="8" spans="1:13">
-      <c r="A8" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="B8" s="7">
+      <c r="A8" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" s="8">
         <v>40</v>
       </c>
-      <c r="C8" s="7">
+      <c r="C8" s="8">
         <v>1</v>
       </c>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7">
+      <c r="D8" s="8"/>
+      <c r="E8" s="8">
         <v>60.4</v>
       </c>
-      <c r="F8" s="7">
+      <c r="F8" s="8">
         <v>61.6</v>
       </c>
-      <c r="G8" s="7">
+      <c r="G8" s="8">
         <v>1.2</v>
       </c>
     </row>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП СПОРТ-ВАРНА/ОП СПОРТ-ВАРНА.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП СПОРТ-ВАРНА/ОП СПОРТ-ВАРНА.xlsx
@@ -173,7 +173,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -183,12 +183,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9EAF7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBDD7EE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -239,17 +233,17 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП СПОРТ-ВАРНА/ОП СПОРТ-ВАРНА.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП СПОРТ-ВАРНА/ОП СПОРТ-ВАРНА.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="26">
   <si>
     <t>Дата</t>
   </si>
@@ -34,9 +34,6 @@
     <t>Литри</t>
   </si>
   <si>
-    <t>Тип количество</t>
-  </si>
-  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -49,76 +46,34 @@
     <t>Сума по ЕКО цена</t>
   </si>
   <si>
-    <t>Час</t>
-  </si>
-  <si>
     <t>Километри</t>
   </si>
   <si>
-    <t>Billing_Document</t>
-  </si>
-  <si>
-    <t>1146 Варна Сливница</t>
+    <t>Варна Сливница</t>
+  </si>
+  <si>
+    <t>ТубаСпорт1</t>
+  </si>
+  <si>
+    <t>В8983ВР</t>
   </si>
   <si>
     <t>В2244РМ</t>
   </si>
   <si>
-    <t>В8983ВР</t>
-  </si>
-  <si>
-    <t>В6330РА</t>
-  </si>
-  <si>
-    <t>ТубаСпорт1</t>
+    <t>78970155027720733</t>
+  </si>
+  <si>
+    <t>78970155027720725</t>
   </si>
   <si>
     <t>78970155027720709</t>
   </si>
   <si>
-    <t>78970155027720725</t>
-  </si>
-  <si>
-    <t>78970155027720717</t>
-  </si>
-  <si>
-    <t>78970155027720733</t>
-  </si>
-  <si>
     <t>95 EKONOMY UNLEADED</t>
   </si>
   <si>
     <t>E GAS LPG</t>
-  </si>
-  <si>
-    <t>DIESEL EKONOMY</t>
-  </si>
-  <si>
-    <t>L15</t>
-  </si>
-  <si>
-    <t>09:08:00</t>
-  </si>
-  <si>
-    <t>11:37:00</t>
-  </si>
-  <si>
-    <t>15:49:00</t>
-  </si>
-  <si>
-    <t>11:48:00</t>
-  </si>
-  <si>
-    <t>3232030826 3232030826</t>
-  </si>
-  <si>
-    <t>3232030872 3232030872</t>
-  </si>
-  <si>
-    <t>3232080516 3232080516</t>
-  </si>
-  <si>
-    <t>3232187143 3232187143</t>
   </si>
   <si>
     <t>Общи литри по продукт / ОП СПОРТ-ВАРНА</t>
@@ -538,7 +493,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N13"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -547,17 +502,14 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="16.7109375" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="11.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:11">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -591,195 +543,150 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" s="3">
+        <v>46174</v>
+      </c>
+      <c r="B2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="C2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="D2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2">
+        <v>20</v>
+      </c>
+      <c r="G2" s="1">
+        <v>1.54</v>
+      </c>
+      <c r="H2">
+        <v>30.8</v>
+      </c>
+      <c r="I2" s="1">
+        <v>1.57</v>
+      </c>
+      <c r="J2">
+        <v>31.4</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="3">
+        <v>46176</v>
+      </c>
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3">
+        <v>20</v>
+      </c>
+      <c r="G3" s="1">
+        <v>1.54</v>
+      </c>
+      <c r="H3">
+        <v>30.8</v>
+      </c>
+      <c r="I3" s="1">
+        <v>1.57</v>
+      </c>
+      <c r="J3">
+        <v>31.4</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" s="3">
+        <v>46183</v>
+      </c>
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14">
-      <c r="A2" s="3">
-        <v>46160</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="D4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4">
+        <v>27.01</v>
+      </c>
+      <c r="G4" s="1">
+        <v>0.7</v>
+      </c>
+      <c r="H4">
+        <v>18.91</v>
+      </c>
+      <c r="I4" s="1">
+        <v>0.71</v>
+      </c>
+      <c r="J4">
+        <v>19.18</v>
+      </c>
+      <c r="K4">
+        <v>67730</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" s="3">
+        <v>46185</v>
+      </c>
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" t="s">
         <v>14</v>
       </c>
-      <c r="C2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F2">
-        <v>49</v>
-      </c>
-      <c r="G2" t="s">
-        <v>26</v>
-      </c>
-      <c r="H2">
-        <v>1.52</v>
-      </c>
-      <c r="I2" s="1">
-        <v>74.48</v>
-      </c>
-      <c r="J2">
-        <v>1.55</v>
-      </c>
-      <c r="K2" s="1">
-        <v>75.95</v>
-      </c>
-      <c r="L2" t="s">
-        <v>27</v>
-      </c>
-      <c r="M2">
-        <v>268415</v>
-      </c>
-      <c r="N2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
-      <c r="A3" s="3">
-        <v>46160</v>
-      </c>
-      <c r="B3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="D5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5">
+        <v>60.4</v>
+      </c>
+      <c r="G5" s="1">
+        <v>1.53</v>
+      </c>
+      <c r="H5">
+        <v>92.41</v>
+      </c>
+      <c r="I5" s="1">
+        <v>1.56</v>
+      </c>
+      <c r="J5">
+        <v>94.22</v>
+      </c>
+      <c r="K5">
+        <v>268935</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" s="4" t="s">
         <v>20</v>
-      </c>
-      <c r="E3" t="s">
-        <v>24</v>
-      </c>
-      <c r="F3">
-        <v>32.54</v>
-      </c>
-      <c r="G3" t="s">
-        <v>26</v>
-      </c>
-      <c r="H3">
-        <v>0.78</v>
-      </c>
-      <c r="I3" s="1">
-        <v>25.38</v>
-      </c>
-      <c r="J3">
-        <v>0.79</v>
-      </c>
-      <c r="K3" s="1">
-        <v>25.71</v>
-      </c>
-      <c r="L3" t="s">
-        <v>28</v>
-      </c>
-      <c r="M3">
-        <v>67501</v>
-      </c>
-      <c r="N3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
-      <c r="A4" s="3">
-        <v>46161</v>
-      </c>
-      <c r="B4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E4" t="s">
-        <v>25</v>
-      </c>
-      <c r="F4">
-        <v>48.9</v>
-      </c>
-      <c r="G4" t="s">
-        <v>26</v>
-      </c>
-      <c r="H4">
-        <v>1.72</v>
-      </c>
-      <c r="I4" s="1">
-        <v>84.11</v>
-      </c>
-      <c r="J4">
-        <v>1.75</v>
-      </c>
-      <c r="K4" s="1">
-        <v>85.58</v>
-      </c>
-      <c r="L4" t="s">
-        <v>29</v>
-      </c>
-      <c r="M4">
-        <v>170725</v>
-      </c>
-      <c r="N4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
-      <c r="A5" s="3">
-        <v>46163</v>
-      </c>
-      <c r="B5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" t="s">
-        <v>22</v>
-      </c>
-      <c r="E5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F5">
-        <v>20</v>
-      </c>
-      <c r="G5" t="s">
-        <v>26</v>
-      </c>
-      <c r="H5">
-        <v>1.54</v>
-      </c>
-      <c r="I5" s="1">
-        <v>30.8</v>
-      </c>
-      <c r="J5">
-        <v>1.57</v>
-      </c>
-      <c r="K5" s="1">
-        <v>31.4</v>
-      </c>
-      <c r="L5" t="s">
-        <v>30</v>
-      </c>
-      <c r="M5">
-        <v>0</v>
-      </c>
-      <c r="N5" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
-      <c r="A8" s="4" t="s">
-        <v>35</v>
       </c>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
@@ -787,102 +694,82 @@
       <c r="E8" s="4"/>
       <c r="F8" s="4"/>
     </row>
-    <row r="9" spans="1:14">
+    <row r="9" spans="1:11">
       <c r="A9" s="5" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
       <c r="A10" s="6" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="B10" s="7">
-        <v>69</v>
+        <v>100.4</v>
       </c>
       <c r="C10" s="7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D10" s="8">
-        <v>1.5258</v>
+        <v>1.534</v>
       </c>
       <c r="E10" s="7">
-        <v>105.28</v>
+        <v>154.01</v>
       </c>
       <c r="F10" s="7">
-        <v>107.35</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
+        <v>157.02</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
       <c r="A11" s="6" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="B11" s="7">
-        <v>48.9</v>
+        <v>27.01</v>
       </c>
       <c r="C11" s="7">
         <v>1</v>
       </c>
       <c r="D11" s="8">
-        <v>1.72</v>
+        <v>0.7000999999999999</v>
       </c>
       <c r="E11" s="7">
-        <v>84.11</v>
+        <v>18.91</v>
       </c>
       <c r="F11" s="7">
-        <v>85.58</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14">
-      <c r="A12" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="B12" s="7">
-        <v>32.54</v>
-      </c>
-      <c r="C12" s="7">
-        <v>1</v>
-      </c>
-      <c r="D12" s="8">
-        <v>0.78</v>
-      </c>
-      <c r="E12" s="7">
-        <v>25.38</v>
-      </c>
-      <c r="F12" s="7">
-        <v>25.71</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14">
-      <c r="A13" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="B13" s="10">
-        <v>150.44</v>
-      </c>
-      <c r="C13" s="10">
+        <v>19.18</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" s="10">
+        <v>127.41</v>
+      </c>
+      <c r="C12" s="10">
         <v>4</v>
       </c>
-      <c r="D13" s="8"/>
-      <c r="E13" s="10">
-        <v>214.77</v>
-      </c>
-      <c r="F13" s="10">
-        <v>218.64</v>
+      <c r="D12" s="8"/>
+      <c r="E12" s="10">
+        <v>172.92</v>
+      </c>
+      <c r="F12" s="10">
+        <v>176.2</v>
       </c>
     </row>
   </sheetData>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП СПОРТ-ВАРНА/ОП СПОРТ-ВАРНА.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП СПОРТ-ВАРНА/ОП СПОРТ-ВАРНА.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="32">
   <si>
     <t>Дата</t>
   </si>
@@ -46,9 +46,15 @@
     <t>Сума по ЕКО цена</t>
   </si>
   <si>
+    <t>Час</t>
+  </si>
+  <si>
     <t>Километри</t>
   </si>
   <si>
+    <t>Billing_Document</t>
+  </si>
+  <si>
     <t>Варна Сливница</t>
   </si>
   <si>
@@ -74,6 +80,18 @@
   </si>
   <si>
     <t>E GAS LPG</t>
+  </si>
+  <si>
+    <t>13:46</t>
+  </si>
+  <si>
+    <t>15:46</t>
+  </si>
+  <si>
+    <t>16:35</t>
+  </si>
+  <si>
+    <t>13:45</t>
   </si>
   <si>
     <t>Общи литри по продукт / ОП СПОРТ-ВАРНА</t>
@@ -493,7 +511,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:M12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -506,10 +524,12 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="11.7109375" customWidth="1"/>
+    <col min="11" max="11" width="7.7109375" customWidth="1"/>
+    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:13">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -543,22 +563,28 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
       <c r="A2" s="3">
         <v>46174</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F2">
         <v>20</v>
@@ -575,25 +601,31 @@
       <c r="J2">
         <v>31.4</v>
       </c>
-      <c r="K2">
+      <c r="K2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:11">
+      <c r="M2">
+        <v>137461</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" s="3">
         <v>46176</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F3">
         <v>20</v>
@@ -610,25 +642,31 @@
       <c r="J3">
         <v>31.4</v>
       </c>
-      <c r="K3">
+      <c r="K3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:11">
+      <c r="M3">
+        <v>138216</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" s="3">
         <v>46183</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F4">
         <v>27.01</v>
@@ -645,25 +683,31 @@
       <c r="J4">
         <v>19.18</v>
       </c>
-      <c r="K4">
+      <c r="K4" t="s">
+        <v>24</v>
+      </c>
+      <c r="L4">
         <v>67730</v>
       </c>
-    </row>
-    <row r="5" spans="1:11">
+      <c r="M4">
+        <v>140695</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5" s="3">
         <v>46185</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D5" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E5" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F5">
         <v>60.4</v>
@@ -680,13 +724,19 @@
       <c r="J5">
         <v>94.22</v>
       </c>
-      <c r="K5">
-        <v>268935</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11">
+      <c r="K5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L5">
+        <v>76644</v>
+      </c>
+      <c r="M5">
+        <v>141389</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
       <c r="A8" s="4" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
@@ -694,18 +744,18 @@
       <c r="E8" s="4"/>
       <c r="F8" s="4"/>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:13">
       <c r="A9" s="5" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="E9" s="5" t="s">
         <v>7</v>
@@ -714,9 +764,9 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:13">
       <c r="A10" s="6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B10" s="7">
         <v>100.4</v>
@@ -734,9 +784,9 @@
         <v>157.02</v>
       </c>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:13">
       <c r="A11" s="6" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B11" s="7">
         <v>27.01</v>
@@ -754,9 +804,9 @@
         <v>19.18</v>
       </c>
     </row>
-    <row r="12" spans="1:11">
+    <row r="12" spans="1:13">
       <c r="A12" s="9" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="B12" s="10">
         <v>127.41</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП СПОРТ-ВАРНА/ОП СПОРТ-ВАРНА.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП СПОРТ-ВАРНА/ОП СПОРТ-ВАРНА.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="30">
   <si>
     <t>Дата</t>
   </si>
@@ -49,49 +49,43 @@
     <t>Час</t>
   </si>
   <si>
-    <t>Километри</t>
-  </si>
-  <si>
-    <t>Billing_Document</t>
-  </si>
-  <si>
     <t>Варна Сливница</t>
   </si>
   <si>
     <t>ТубаСпорт1</t>
   </si>
   <si>
+    <t>В6330РА</t>
+  </si>
+  <si>
     <t>В8983ВР</t>
   </si>
   <si>
-    <t>В2244РМ</t>
-  </si>
-  <si>
     <t>78970155027720733</t>
   </si>
   <si>
+    <t>78970155027720717</t>
+  </si>
+  <si>
     <t>78970155027720725</t>
   </si>
   <si>
-    <t>78970155027720709</t>
-  </si>
-  <si>
     <t>95 EKONOMY UNLEADED</t>
   </si>
   <si>
+    <t>DIESEL EKONOMY</t>
+  </si>
+  <si>
     <t>E GAS LPG</t>
   </si>
   <si>
-    <t>13:46</t>
-  </si>
-  <si>
-    <t>15:46</t>
-  </si>
-  <si>
-    <t>16:35</t>
-  </si>
-  <si>
-    <t>13:45</t>
+    <t>2026-06-18 16:23:29</t>
+  </si>
+  <si>
+    <t>2026-06-19 09:43:35</t>
+  </si>
+  <si>
+    <t>2026-06-25 11:34:47</t>
   </si>
   <si>
     <t>Общи литри по продукт / ОП СПОРТ-ВАРНА</t>
@@ -511,7 +505,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -524,12 +518,10 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="7.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="11" max="11" width="21.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:11">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -563,268 +555,223 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" s="3">
+        <v>46191</v>
+      </c>
+      <c r="B2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="C2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="3">
-        <v>46174</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="D2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2">
+        <v>40</v>
+      </c>
+      <c r="G2" s="1">
+        <v>1.52</v>
+      </c>
+      <c r="H2">
+        <v>60.8</v>
+      </c>
+      <c r="I2" s="1">
+        <v>1.55</v>
+      </c>
+      <c r="J2">
+        <v>62</v>
+      </c>
+      <c r="K2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="3">
+        <v>46192</v>
+      </c>
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" t="s">
         <v>13</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3">
+        <v>43.53</v>
+      </c>
+      <c r="G3" s="1">
+        <v>1.53</v>
+      </c>
+      <c r="H3">
+        <v>66.59999999999999</v>
+      </c>
+      <c r="I3" s="1">
+        <v>1.56</v>
+      </c>
+      <c r="J3">
+        <v>67.91</v>
+      </c>
+      <c r="K3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" s="3">
+        <v>46198</v>
+      </c>
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" t="s">
         <v>14</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D4" t="s">
         <v>17</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E4" t="s">
         <v>20</v>
       </c>
-      <c r="F2">
+      <c r="F4">
+        <v>26.59</v>
+      </c>
+      <c r="G4" s="1">
+        <v>0.65</v>
+      </c>
+      <c r="H4">
+        <v>17.28</v>
+      </c>
+      <c r="I4" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="J4">
+        <v>17.55</v>
+      </c>
+      <c r="K4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" s="7">
+        <v>43.53</v>
+      </c>
+      <c r="C9" s="7">
+        <v>1</v>
+      </c>
+      <c r="D9" s="8">
+        <v>1.53</v>
+      </c>
+      <c r="E9" s="7">
+        <v>66.59999999999999</v>
+      </c>
+      <c r="F9" s="7">
+        <v>67.91</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" s="7">
+        <v>40</v>
+      </c>
+      <c r="C10" s="7">
+        <v>1</v>
+      </c>
+      <c r="D10" s="8">
+        <v>1.52</v>
+      </c>
+      <c r="E10" s="7">
+        <v>60.8</v>
+      </c>
+      <c r="F10" s="7">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="G2" s="1">
-        <v>1.54</v>
-      </c>
-      <c r="H2">
-        <v>30.8</v>
-      </c>
-      <c r="I2" s="1">
-        <v>1.57</v>
-      </c>
-      <c r="J2">
-        <v>31.4</v>
-      </c>
-      <c r="K2" t="s">
-        <v>22</v>
-      </c>
-      <c r="L2">
-        <v>0</v>
-      </c>
-      <c r="M2">
-        <v>137461</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="3">
-        <v>46176</v>
-      </c>
-      <c r="B3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F3">
-        <v>20</v>
-      </c>
-      <c r="G3" s="1">
-        <v>1.54</v>
-      </c>
-      <c r="H3">
-        <v>30.8</v>
-      </c>
-      <c r="I3" s="1">
-        <v>1.57</v>
-      </c>
-      <c r="J3">
-        <v>31.4</v>
-      </c>
-      <c r="K3" t="s">
-        <v>23</v>
-      </c>
-      <c r="L3">
-        <v>0</v>
-      </c>
-      <c r="M3">
-        <v>138216</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="3">
-        <v>46183</v>
-      </c>
-      <c r="B4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" t="s">
-        <v>21</v>
-      </c>
-      <c r="F4">
-        <v>27.01</v>
-      </c>
-      <c r="G4" s="1">
-        <v>0.7</v>
-      </c>
-      <c r="H4">
-        <v>18.91</v>
-      </c>
-      <c r="I4" s="1">
-        <v>0.71</v>
-      </c>
-      <c r="J4">
-        <v>19.18</v>
-      </c>
-      <c r="K4" t="s">
-        <v>24</v>
-      </c>
-      <c r="L4">
-        <v>67730</v>
-      </c>
-      <c r="M4">
-        <v>140695</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="3">
-        <v>46185</v>
-      </c>
-      <c r="B5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E5" t="s">
-        <v>20</v>
-      </c>
-      <c r="F5">
-        <v>60.4</v>
-      </c>
-      <c r="G5" s="1">
-        <v>1.53</v>
-      </c>
-      <c r="H5">
-        <v>92.41</v>
-      </c>
-      <c r="I5" s="1">
-        <v>1.56</v>
-      </c>
-      <c r="J5">
-        <v>94.22</v>
-      </c>
-      <c r="K5" t="s">
-        <v>25</v>
-      </c>
-      <c r="L5">
-        <v>76644</v>
-      </c>
-      <c r="M5">
-        <v>141389</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="A10" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="B10" s="7">
-        <v>100.4</v>
-      </c>
-      <c r="C10" s="7">
-        <v>3</v>
-      </c>
-      <c r="D10" s="8">
-        <v>1.534</v>
-      </c>
-      <c r="E10" s="7">
-        <v>154.01</v>
-      </c>
-      <c r="F10" s="7">
-        <v>157.02</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13">
-      <c r="A11" s="6" t="s">
-        <v>21</v>
-      </c>
       <c r="B11" s="7">
-        <v>27.01</v>
+        <v>26.59</v>
       </c>
       <c r="C11" s="7">
         <v>1</v>
       </c>
       <c r="D11" s="8">
-        <v>0.7000999999999999</v>
+        <v>0.6499</v>
       </c>
       <c r="E11" s="7">
-        <v>18.91</v>
+        <v>17.28</v>
       </c>
       <c r="F11" s="7">
-        <v>19.18</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13">
+        <v>17.55</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
       <c r="A12" s="9" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B12" s="10">
-        <v>127.41</v>
+        <v>110.12</v>
       </c>
       <c r="C12" s="10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D12" s="8"/>
       <c r="E12" s="10">
-        <v>172.92</v>
+        <v>144.68</v>
       </c>
       <c r="F12" s="10">
-        <v>176.2</v>
+        <v>147.46</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="A7:F7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП СПОРТ-ВАРНА/ОП СПОРТ-ВАРНА.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП СПОРТ-ВАРНА/ОП СПОРТ-ВАРНА.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="37">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -49,7 +52,13 @@
     <t>Час</t>
   </si>
   <si>
-    <t>Варна Сливница</t>
+    <t>Километри</t>
+  </si>
+  <si>
+    <t>Billing_Document</t>
+  </si>
+  <si>
+    <t>1146 Варна Сливница</t>
   </si>
   <si>
     <t>ТубаСпорт1</t>
@@ -79,13 +88,25 @@
     <t>E GAS LPG</t>
   </si>
   <si>
-    <t>2026-06-18 16:23:29</t>
-  </si>
-  <si>
-    <t>2026-06-19 09:43:35</t>
-  </si>
-  <si>
-    <t>2026-06-25 11:34:47</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>16:23:00</t>
+  </si>
+  <si>
+    <t>09:44:00</t>
+  </si>
+  <si>
+    <t>11:35:00</t>
+  </si>
+  <si>
+    <t>3233508800 3233508800</t>
+  </si>
+  <si>
+    <t>3233569305 3233569305</t>
+  </si>
+  <si>
+    <t>3233832754 3233832754</t>
   </si>
   <si>
     <t>Общи литри по продукт / ОП СПОРТ-ВАРНА</t>
@@ -505,7 +526,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:N12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -514,14 +535,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="21.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -555,115 +579,151 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" s="3">
         <v>46191</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F2">
         <v>40</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H2">
         <v>1.52</v>
       </c>
-      <c r="H2">
+      <c r="I2" s="1">
         <v>60.8</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2">
         <v>1.55</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="1">
         <v>62</v>
       </c>
-      <c r="K2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
+      <c r="L2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" s="3">
         <v>46192</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D3" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E3" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F3">
         <v>43.53</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H3">
         <v>1.53</v>
       </c>
-      <c r="H3">
+      <c r="I3" s="1">
         <v>66.59999999999999</v>
       </c>
-      <c r="I3" s="1">
+      <c r="J3">
         <v>1.56</v>
       </c>
-      <c r="J3">
+      <c r="K3" s="1">
         <v>67.91</v>
       </c>
-      <c r="K3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
+      <c r="L3" t="s">
+        <v>26</v>
+      </c>
+      <c r="M3">
+        <v>171391</v>
+      </c>
+      <c r="N3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" s="3">
         <v>46198</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D4" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E4" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F4">
         <v>26.59</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H4">
         <v>0.65</v>
       </c>
-      <c r="H4">
+      <c r="I4" s="1">
         <v>17.28</v>
       </c>
-      <c r="I4" s="1">
+      <c r="J4">
         <v>0.66</v>
       </c>
-      <c r="J4">
+      <c r="K4" s="1">
         <v>17.55</v>
       </c>
-      <c r="K4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11">
+      <c r="L4" t="s">
+        <v>27</v>
+      </c>
+      <c r="M4">
+        <v>67964</v>
+      </c>
+      <c r="N4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" s="4" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
@@ -671,29 +731,29 @@
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:14">
       <c r="A8" s="5" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9" s="6" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B9" s="7">
         <v>43.53</v>
@@ -711,9 +771,9 @@
         <v>67.91</v>
       </c>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:14">
       <c r="A10" s="6" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B10" s="7">
         <v>40</v>
@@ -731,9 +791,9 @@
         <v>62</v>
       </c>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:14">
       <c r="A11" s="6" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B11" s="7">
         <v>26.59</v>
@@ -751,9 +811,9 @@
         <v>17.55</v>
       </c>
     </row>
-    <row r="12" spans="1:11">
+    <row r="12" spans="1:14">
       <c r="A12" s="9" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="B12" s="10">
         <v>110.12</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП СПОРТ-ВАРНА/ОП СПОРТ-ВАРНА.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП СПОРТ-ВАРНА/ОП СПОРТ-ВАРНА.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="32">
   <si>
     <t>Дата</t>
   </si>
@@ -34,9 +34,6 @@
     <t>Литри</t>
   </si>
   <si>
-    <t>Тип количество</t>
-  </si>
-  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -58,7 +55,7 @@
     <t>Billing_Document</t>
   </si>
   <si>
-    <t>1146 Варна Сливница</t>
+    <t>Варна Сливница</t>
   </si>
   <si>
     <t>ТубаСпорт1</t>
@@ -88,25 +85,13 @@
     <t>E GAS LPG</t>
   </si>
   <si>
-    <t>L15</t>
-  </si>
-  <si>
-    <t>16:23:00</t>
-  </si>
-  <si>
-    <t>09:44:00</t>
-  </si>
-  <si>
-    <t>11:35:00</t>
-  </si>
-  <si>
-    <t>3233508800 3233508800</t>
-  </si>
-  <si>
-    <t>3233569305 3233569305</t>
-  </si>
-  <si>
-    <t>3233832754 3233832754</t>
+    <t>16:23</t>
+  </si>
+  <si>
+    <t>09:43</t>
+  </si>
+  <si>
+    <t>11:34</t>
   </si>
   <si>
     <t>Общи литри по продукт / ОП СПОРТ-ВАРНА</t>
@@ -526,7 +511,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N12"/>
+  <dimension ref="A1:M12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -535,17 +520,16 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="16.7109375" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="7.7109375" customWidth="1"/>
+    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:13">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -585,145 +569,133 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14">
+    </row>
+    <row r="2" spans="1:13">
       <c r="A2" s="3">
         <v>46191</v>
       </c>
       <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="s">
         <v>14</v>
       </c>
-      <c r="C2" t="s">
-        <v>15</v>
-      </c>
       <c r="D2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F2">
         <v>40</v>
       </c>
-      <c r="G2" t="s">
-        <v>24</v>
+      <c r="G2" s="1">
+        <v>1.52</v>
       </c>
       <c r="H2">
-        <v>1.52</v>
+        <v>60.8</v>
       </c>
       <c r="I2" s="1">
-        <v>60.8</v>
+        <v>1.55</v>
       </c>
       <c r="J2">
-        <v>1.55</v>
-      </c>
-      <c r="K2" s="1">
         <v>62</v>
       </c>
-      <c r="L2" t="s">
-        <v>25</v>
+      <c r="K2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
       </c>
       <c r="M2">
-        <v>0</v>
-      </c>
-      <c r="N2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
+        <v>143522</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" s="3">
         <v>46192</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F3">
         <v>43.53</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" s="1">
+        <v>1.53</v>
+      </c>
+      <c r="H3">
+        <v>66.59999999999999</v>
+      </c>
+      <c r="I3" s="1">
+        <v>1.56</v>
+      </c>
+      <c r="J3">
+        <v>67.91</v>
+      </c>
+      <c r="K3" t="s">
         <v>24</v>
       </c>
-      <c r="H3">
-        <v>1.53</v>
-      </c>
-      <c r="I3" s="1">
-        <v>66.59999999999999</v>
-      </c>
-      <c r="J3">
-        <v>1.56</v>
-      </c>
-      <c r="K3" s="1">
-        <v>67.91</v>
-      </c>
-      <c r="L3" t="s">
-        <v>26</v>
+      <c r="L3">
+        <v>171391</v>
       </c>
       <c r="M3">
-        <v>171391</v>
-      </c>
-      <c r="N3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
+        <v>143688</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" s="3">
         <v>46198</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F4">
         <v>26.59</v>
       </c>
-      <c r="G4" t="s">
-        <v>24</v>
+      <c r="G4" s="1">
+        <v>0.65</v>
       </c>
       <c r="H4">
-        <v>0.65</v>
+        <v>17.28</v>
       </c>
       <c r="I4" s="1">
-        <v>17.28</v>
+        <v>0.66</v>
       </c>
       <c r="J4">
-        <v>0.66</v>
-      </c>
-      <c r="K4" s="1">
         <v>17.55</v>
       </c>
-      <c r="L4" t="s">
-        <v>27</v>
+      <c r="K4" t="s">
+        <v>25</v>
+      </c>
+      <c r="L4">
+        <v>67964</v>
       </c>
       <c r="M4">
-        <v>67964</v>
-      </c>
-      <c r="N4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
+        <v>145551</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
       <c r="A7" s="4" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
@@ -731,29 +703,29 @@
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
     </row>
-    <row r="8" spans="1:14">
+    <row r="8" spans="1:13">
       <c r="A8" s="5" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
       <c r="A9" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B9" s="7">
         <v>43.53</v>
@@ -771,9 +743,9 @@
         <v>67.91</v>
       </c>
     </row>
-    <row r="10" spans="1:14">
+    <row r="10" spans="1:13">
       <c r="A10" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B10" s="7">
         <v>40</v>
@@ -791,9 +763,9 @@
         <v>62</v>
       </c>
     </row>
-    <row r="11" spans="1:14">
+    <row r="11" spans="1:13">
       <c r="A11" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B11" s="7">
         <v>26.59</v>
@@ -811,9 +783,9 @@
         <v>17.55</v>
       </c>
     </row>
-    <row r="12" spans="1:14">
+    <row r="12" spans="1:13">
       <c r="A12" s="9" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B12" s="10">
         <v>110.12</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП СПОРТ-ВАРНА/ОП СПОРТ-ВАРНА.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП СПОРТ-ВАРНА/ОП СПОРТ-ВАРНА.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="40">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -52,13 +55,16 @@
     <t>Километри</t>
   </si>
   <si>
-    <t>Варна Порт</t>
-  </si>
-  <si>
-    <t>Варна</t>
-  </si>
-  <si>
-    <t>Варна Сливница</t>
+    <t>Billing_Document</t>
+  </si>
+  <si>
+    <t>1148 Варна пристанище</t>
+  </si>
+  <si>
+    <t>1146 Варна Сливница</t>
+  </si>
+  <si>
+    <t>В6330РА</t>
   </si>
   <si>
     <t>ТубаСпорт1</t>
@@ -67,7 +73,7 @@
     <t>В8983ВР</t>
   </si>
   <si>
-    <t>В2244РМ</t>
+    <t>78970155027720717</t>
   </si>
   <si>
     <t>78970155027720733</t>
@@ -76,7 +82,7 @@
     <t>78970155027720725</t>
   </si>
   <si>
-    <t>78970155027720709</t>
+    <t>DIESEL EKONOMY</t>
   </si>
   <si>
     <t>95 EKONOMY UNLEADED</t>
@@ -85,16 +91,31 @@
     <t>E GAS LPG</t>
   </si>
   <si>
-    <t>2026-07-02 10:14:28</t>
-  </si>
-  <si>
-    <t>2026-07-13 12:11:10</t>
-  </si>
-  <si>
-    <t>2026-07-14 14:16:10</t>
-  </si>
-  <si>
-    <t>2026-07-15 12:00:30</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>11:51:00</t>
+  </si>
+  <si>
+    <t>14:28:00</t>
+  </si>
+  <si>
+    <t>14:54:00</t>
+  </si>
+  <si>
+    <t>13:59:00</t>
+  </si>
+  <si>
+    <t>3234948009 3234948009</t>
+  </si>
+  <si>
+    <t>3235464501 3235464501</t>
+  </si>
+  <si>
+    <t>3235622053 3235622053</t>
+  </si>
+  <si>
+    <t>3235636388 3235636388</t>
   </si>
   <si>
     <t>Общи литри по продукт / ОП СПОРТ-ВАРНА</t>
@@ -514,7 +535,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:N13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -523,15 +544,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="21.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -568,162 +591,192 @@
       <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:12">
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" s="3">
-        <v>46205</v>
+        <v>46220</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2">
+        <v>52</v>
+      </c>
+      <c r="G2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H2">
+        <v>1.6</v>
+      </c>
+      <c r="I2" s="1">
+        <v>83.2</v>
+      </c>
+      <c r="J2">
+        <v>1.63</v>
+      </c>
+      <c r="K2" s="1">
+        <v>84.76000000000001</v>
+      </c>
+      <c r="L2" t="s">
+        <v>26</v>
+      </c>
+      <c r="M2">
+        <v>171900</v>
+      </c>
+      <c r="N2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" s="3">
+        <v>46231</v>
+      </c>
+      <c r="B3" t="s">
         <v>15</v>
       </c>
-      <c r="D2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F2">
-        <v>39.99</v>
-      </c>
-      <c r="G2" s="1">
-        <v>1.47</v>
-      </c>
-      <c r="H2">
-        <v>58.79</v>
-      </c>
-      <c r="I2" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="J2">
-        <v>59.98</v>
-      </c>
-      <c r="K2" t="s">
+      <c r="C3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" t="s">
         <v>23</v>
       </c>
-      <c r="L2">
+      <c r="F3">
+        <v>40</v>
+      </c>
+      <c r="G3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H3">
+        <v>1.53</v>
+      </c>
+      <c r="I3" s="1">
+        <v>61.2</v>
+      </c>
+      <c r="J3">
+        <v>1.56</v>
+      </c>
+      <c r="K3" s="1">
+        <v>62.4</v>
+      </c>
+      <c r="L3" t="s">
+        <v>27</v>
+      </c>
+      <c r="M3">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:12">
-      <c r="A3" s="3">
-        <v>46216</v>
-      </c>
-      <c r="B3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="N3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" s="3">
+        <v>46234</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="s">
         <v>16</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D4" t="s">
         <v>19</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E4" t="s">
         <v>22</v>
       </c>
-      <c r="F3">
-        <v>29.51</v>
-      </c>
-      <c r="G3" s="1">
-        <v>0.62</v>
-      </c>
-      <c r="H3">
-        <v>18.3</v>
-      </c>
-      <c r="I3" s="1">
-        <v>0.63</v>
-      </c>
-      <c r="J3">
-        <v>18.59</v>
-      </c>
-      <c r="K3" t="s">
-        <v>24</v>
-      </c>
-      <c r="L3">
-        <v>68165</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12">
-      <c r="A4" s="3">
-        <v>46217</v>
-      </c>
-      <c r="B4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E4" t="s">
-        <v>21</v>
-      </c>
       <c r="F4">
-        <v>62.97</v>
-      </c>
-      <c r="G4" s="1">
-        <v>1.46</v>
+        <v>35.7</v>
+      </c>
+      <c r="G4" t="s">
+        <v>25</v>
       </c>
       <c r="H4">
-        <v>91.94</v>
+        <v>1.74</v>
       </c>
       <c r="I4" s="1">
-        <v>1.49</v>
+        <v>62.12</v>
       </c>
       <c r="J4">
-        <v>93.83</v>
-      </c>
-      <c r="K4" t="s">
-        <v>25</v>
-      </c>
-      <c r="L4">
-        <v>269380</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
+        <v>1.77</v>
+      </c>
+      <c r="K4" s="1">
+        <v>63.19</v>
+      </c>
+      <c r="L4" t="s">
+        <v>28</v>
+      </c>
+      <c r="M4">
+        <v>172250</v>
+      </c>
+      <c r="N4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" s="3">
-        <v>46218</v>
+        <v>46234</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D5" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F5">
-        <v>40</v>
-      </c>
-      <c r="G5" s="1">
-        <v>1.46</v>
+        <v>19.56</v>
+      </c>
+      <c r="G5" t="s">
+        <v>25</v>
       </c>
       <c r="H5">
-        <v>58.4</v>
+        <v>0.63</v>
       </c>
       <c r="I5" s="1">
-        <v>1.49</v>
+        <v>12.32</v>
       </c>
       <c r="J5">
-        <v>59.6</v>
-      </c>
-      <c r="K5" t="s">
-        <v>26</v>
-      </c>
-      <c r="L5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12">
+        <v>0.64</v>
+      </c>
+      <c r="K5" s="1">
+        <v>12.52</v>
+      </c>
+      <c r="L5" t="s">
+        <v>29</v>
+      </c>
+      <c r="M5">
+        <v>68303</v>
+      </c>
+      <c r="N5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" s="4" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
@@ -731,82 +784,102 @@
       <c r="E8" s="4"/>
       <c r="F8" s="4"/>
     </row>
-    <row r="9" spans="1:12">
+    <row r="9" spans="1:14">
       <c r="A9" s="5" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B10" s="7">
-        <v>142.96</v>
+        <v>87.7</v>
       </c>
       <c r="C10" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D10" s="8">
-        <v>1.4629</v>
+        <v>1.657</v>
       </c>
       <c r="E10" s="7">
-        <v>209.13</v>
+        <v>145.32</v>
       </c>
       <c r="F10" s="7">
-        <v>213.41</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12">
+        <v>147.95</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B11" s="7">
-        <v>29.51</v>
+        <v>40</v>
       </c>
       <c r="C11" s="7">
         <v>1</v>
       </c>
       <c r="D11" s="8">
-        <v>0.6201</v>
+        <v>1.53</v>
       </c>
       <c r="E11" s="7">
-        <v>18.3</v>
+        <v>61.2</v>
       </c>
       <c r="F11" s="7">
-        <v>18.59</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12">
-      <c r="A12" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="B12" s="10">
-        <v>172.47</v>
-      </c>
-      <c r="C12" s="10">
+        <v>62.4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B12" s="7">
+        <v>19.56</v>
+      </c>
+      <c r="C12" s="7">
+        <v>1</v>
+      </c>
+      <c r="D12" s="8">
+        <v>0.6299</v>
+      </c>
+      <c r="E12" s="7">
+        <v>12.32</v>
+      </c>
+      <c r="F12" s="7">
+        <v>12.52</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="B13" s="10">
+        <v>147.26</v>
+      </c>
+      <c r="C13" s="10">
         <v>4</v>
       </c>
-      <c r="D12" s="8"/>
-      <c r="E12" s="10">
-        <v>227.43</v>
-      </c>
-      <c r="F12" s="10">
-        <v>232</v>
+      <c r="D13" s="8"/>
+      <c r="E13" s="10">
+        <v>218.84</v>
+      </c>
+      <c r="F13" s="10">
+        <v>222.87</v>
       </c>
     </row>
   </sheetData>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП СПОРТ-ВАРНА/ОП СПОРТ-ВАРНА.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП СПОРТ-ВАРНА/ОП СПОРТ-ВАРНА.xlsx
@@ -143,7 +143,7 @@
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="#,##0.00"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="166" formatCode="#,##0.000000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -815,7 +815,7 @@
         <v>2</v>
       </c>
       <c r="D10" s="8">
-        <v>1.657</v>
+        <v>1.657013</v>
       </c>
       <c r="E10" s="7">
         <v>145.32</v>
@@ -855,7 +855,7 @@
         <v>1</v>
       </c>
       <c r="D12" s="8">
-        <v>0.6299</v>
+        <v>0.629857</v>
       </c>
       <c r="E12" s="7">
         <v>12.32</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП СПОРТ-ВАРНА/ОП СПОРТ-ВАРНА.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП СПОРТ-ВАРНА/ОП СПОРТ-ВАРНА.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="41">
   <si>
     <t>Дата</t>
   </si>
@@ -35,6 +35,9 @@
   </si>
   <si>
     <t>Тип количество</t>
+  </si>
+  <si>
+    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -535,7 +538,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N13"/>
+  <dimension ref="A1:O13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -548,13 +551,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
+    <col min="13" max="13" width="10.7109375" customWidth="1"/>
+    <col min="14" max="14" width="11.7109375" customWidth="1"/>
+    <col min="15" max="15" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:15">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -597,186 +600,201 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14">
+      <c r="O1" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
       <c r="A2" s="3">
         <v>46220</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F2">
         <v>52</v>
       </c>
       <c r="G2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H2">
+        <v>1.499</v>
+      </c>
+      <c r="I2" s="1">
         <v>1.6</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2">
         <v>83.2</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="1">
         <v>1.63</v>
       </c>
-      <c r="K2" s="1">
+      <c r="L2" s="1">
         <v>84.76000000000001</v>
       </c>
-      <c r="L2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M2">
+      <c r="M2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N2">
         <v>171900</v>
       </c>
-      <c r="N2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
+      <c r="O2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
       <c r="A3" s="3">
         <v>46231</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F3">
         <v>40</v>
       </c>
       <c r="G3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H3">
+        <v>1.441</v>
+      </c>
+      <c r="I3" s="1">
         <v>1.53</v>
       </c>
-      <c r="I3" s="1">
+      <c r="J3">
         <v>61.2</v>
       </c>
-      <c r="J3">
+      <c r="K3" s="1">
         <v>1.56</v>
       </c>
-      <c r="K3" s="1">
+      <c r="L3" s="1">
         <v>62.4</v>
       </c>
-      <c r="L3" t="s">
-        <v>27</v>
-      </c>
-      <c r="M3">
+      <c r="M3" t="s">
+        <v>28</v>
+      </c>
+      <c r="N3">
         <v>0</v>
       </c>
-      <c r="N3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
+      <c r="O3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
       <c r="A4" s="3">
         <v>46234</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F4">
-        <v>35.7</v>
+        <v>35.701</v>
       </c>
       <c r="G4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H4">
+        <v>1.689</v>
+      </c>
+      <c r="I4" s="1">
         <v>1.74</v>
       </c>
-      <c r="I4" s="1">
-        <v>62.12</v>
-      </c>
       <c r="J4">
+        <v>62.11974</v>
+      </c>
+      <c r="K4" s="1">
         <v>1.77</v>
       </c>
-      <c r="K4" s="1">
-        <v>63.19</v>
-      </c>
-      <c r="L4" t="s">
-        <v>28</v>
-      </c>
-      <c r="M4">
+      <c r="L4" s="1">
+        <v>63.19077</v>
+      </c>
+      <c r="M4" t="s">
+        <v>29</v>
+      </c>
+      <c r="N4">
         <v>172250</v>
       </c>
-      <c r="N4" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
+      <c r="O4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
       <c r="A5" s="3">
         <v>46234</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F5">
-        <v>19.56</v>
+        <v>19.563</v>
       </c>
       <c r="G5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5" s="1">
         <v>0.63</v>
       </c>
-      <c r="I5" s="1">
-        <v>12.32</v>
-      </c>
       <c r="J5">
+        <v>12.32469</v>
+      </c>
+      <c r="K5" s="1">
         <v>0.64</v>
       </c>
-      <c r="K5" s="1">
-        <v>12.52</v>
-      </c>
-      <c r="L5" t="s">
-        <v>29</v>
-      </c>
-      <c r="M5">
+      <c r="L5" s="1">
+        <v>12.52032</v>
+      </c>
+      <c r="M5" t="s">
+        <v>30</v>
+      </c>
+      <c r="N5">
         <v>68303</v>
       </c>
-      <c r="N5" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
+      <c r="O5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
       <c r="A8" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
@@ -784,38 +802,38 @@
       <c r="E8" s="4"/>
       <c r="F8" s="4"/>
     </row>
-    <row r="9" spans="1:14">
+    <row r="9" spans="1:15">
       <c r="A9" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15">
       <c r="A10" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B10" s="7">
-        <v>87.7</v>
+        <v>87.70099999999999</v>
       </c>
       <c r="C10" s="7">
         <v>2</v>
       </c>
       <c r="D10" s="8">
-        <v>1.657013</v>
+        <v>1.656991</v>
       </c>
       <c r="E10" s="7">
         <v>145.32</v>
@@ -824,9 +842,9 @@
         <v>147.95</v>
       </c>
     </row>
-    <row r="11" spans="1:14">
+    <row r="11" spans="1:15">
       <c r="A11" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B11" s="7">
         <v>40</v>
@@ -844,18 +862,18 @@
         <v>62.4</v>
       </c>
     </row>
-    <row r="12" spans="1:14">
+    <row r="12" spans="1:15">
       <c r="A12" s="6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B12" s="7">
-        <v>19.56</v>
+        <v>19.563</v>
       </c>
       <c r="C12" s="7">
         <v>1</v>
       </c>
       <c r="D12" s="8">
-        <v>0.629857</v>
+        <v>0.63</v>
       </c>
       <c r="E12" s="7">
         <v>12.32</v>
@@ -864,12 +882,12 @@
         <v>12.52</v>
       </c>
     </row>
-    <row r="13" spans="1:14">
+    <row r="13" spans="1:15">
       <c r="A13" s="9" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B13" s="10">
-        <v>147.26</v>
+        <v>147.264</v>
       </c>
       <c r="C13" s="10">
         <v>4</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП СПОРТ-ВАРНА/ОП СПОРТ-ВАРНА.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП СПОРТ-ВАРНА/ОП СПОРТ-ВАРНА.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="40">
   <si>
     <t>Дата</t>
   </si>
@@ -35,9 +35,6 @@
   </si>
   <si>
     <t>Тип количество</t>
-  </si>
-  <si>
-    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -144,9 +141,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="#,##0.00"/>
+    <numFmt numFmtId="164" formatCode="#,##0.000"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="#,##0.000000"/>
+    <numFmt numFmtId="166" formatCode="#,##0.00"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -240,10 +237,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -538,7 +535,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O13"/>
+  <dimension ref="A1:N13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -551,13 +548,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
-    <col min="13" max="13" width="10.7109375" customWidth="1"/>
-    <col min="14" max="14" width="11.7109375" customWidth="1"/>
-    <col min="15" max="15" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -600,201 +597,186 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15">
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" s="3">
         <v>46220</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F2">
         <v>52</v>
       </c>
       <c r="G2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H2">
+        <v>1.6</v>
+      </c>
+      <c r="I2" s="1">
+        <v>83.2</v>
+      </c>
+      <c r="J2">
+        <v>1.63</v>
+      </c>
+      <c r="K2" s="1">
+        <v>84.76000000000001</v>
+      </c>
+      <c r="L2" t="s">
         <v>26</v>
       </c>
-      <c r="H2">
-        <v>1.499</v>
-      </c>
-      <c r="I2" s="1">
-        <v>1.6</v>
-      </c>
-      <c r="J2">
-        <v>83.2</v>
-      </c>
-      <c r="K2" s="1">
-        <v>1.63</v>
-      </c>
-      <c r="L2" s="1">
-        <v>84.76000000000001</v>
-      </c>
-      <c r="M2" t="s">
-        <v>27</v>
-      </c>
-      <c r="N2">
+      <c r="M2">
         <v>171900</v>
       </c>
-      <c r="O2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15">
+      <c r="N2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" s="3">
         <v>46231</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F3">
         <v>40</v>
       </c>
       <c r="G3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H3">
-        <v>1.441</v>
+        <v>1.53</v>
       </c>
       <c r="I3" s="1">
-        <v>1.53</v>
+        <v>61.2</v>
       </c>
       <c r="J3">
-        <v>61.2</v>
+        <v>1.56</v>
       </c>
       <c r="K3" s="1">
-        <v>1.56</v>
-      </c>
-      <c r="L3" s="1">
         <v>62.4</v>
       </c>
-      <c r="M3" t="s">
-        <v>28</v>
-      </c>
-      <c r="N3">
+      <c r="L3" t="s">
+        <v>27</v>
+      </c>
+      <c r="M3">
         <v>0</v>
       </c>
-      <c r="O3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15">
+      <c r="N3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" s="3">
         <v>46234</v>
       </c>
       <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="s">
         <v>16</v>
       </c>
-      <c r="C4" t="s">
-        <v>17</v>
-      </c>
       <c r="D4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F4">
         <v>35.701</v>
       </c>
       <c r="G4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H4">
-        <v>1.689</v>
+        <v>1.74</v>
       </c>
       <c r="I4" s="1">
-        <v>1.74</v>
+        <v>62.12</v>
       </c>
       <c r="J4">
-        <v>62.11974</v>
+        <v>1.77</v>
       </c>
       <c r="K4" s="1">
-        <v>1.77</v>
-      </c>
-      <c r="L4" s="1">
-        <v>63.19077</v>
-      </c>
-      <c r="M4" t="s">
-        <v>29</v>
-      </c>
-      <c r="N4">
+        <v>63.191</v>
+      </c>
+      <c r="L4" t="s">
+        <v>28</v>
+      </c>
+      <c r="M4">
         <v>172250</v>
       </c>
-      <c r="O4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15">
+      <c r="N4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" s="3">
         <v>46234</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F5">
         <v>19.563</v>
       </c>
       <c r="G5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H5">
-        <v>1</v>
+        <v>0.63</v>
       </c>
       <c r="I5" s="1">
-        <v>0.63</v>
+        <v>12.325</v>
       </c>
       <c r="J5">
-        <v>12.32469</v>
+        <v>0.64</v>
       </c>
       <c r="K5" s="1">
-        <v>0.64</v>
-      </c>
-      <c r="L5" s="1">
-        <v>12.52032</v>
-      </c>
-      <c r="M5" t="s">
-        <v>30</v>
-      </c>
-      <c r="N5">
+        <v>12.52</v>
+      </c>
+      <c r="L5" t="s">
+        <v>29</v>
+      </c>
+      <c r="M5">
         <v>68303</v>
       </c>
-      <c r="O5" t="s">
+      <c r="N5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" s="4" t="s">
         <v>34</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15">
-      <c r="A8" s="4" t="s">
-        <v>35</v>
       </c>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
@@ -802,89 +784,89 @@
       <c r="E8" s="4"/>
       <c r="F8" s="4"/>
     </row>
-    <row r="9" spans="1:15">
+    <row r="9" spans="1:14">
       <c r="A9" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="C9" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="D9" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D9" s="5" t="s">
-        <v>39</v>
-      </c>
       <c r="E9" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B10" s="7">
         <v>87.70099999999999</v>
       </c>
-      <c r="C10" s="7">
+      <c r="C10" s="8">
         <v>2</v>
       </c>
       <c r="D10" s="8">
-        <v>1.656991</v>
-      </c>
-      <c r="E10" s="7">
+        <v>1.657</v>
+      </c>
+      <c r="E10" s="8">
         <v>145.32</v>
       </c>
-      <c r="F10" s="7">
-        <v>147.95</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15">
+      <c r="F10" s="8">
+        <v>147.951</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B11" s="7">
         <v>40</v>
       </c>
-      <c r="C11" s="7">
+      <c r="C11" s="8">
         <v>1</v>
       </c>
       <c r="D11" s="8">
         <v>1.53</v>
       </c>
-      <c r="E11" s="7">
+      <c r="E11" s="8">
         <v>61.2</v>
       </c>
-      <c r="F11" s="7">
+      <c r="F11" s="8">
         <v>62.4</v>
       </c>
     </row>
-    <row r="12" spans="1:15">
+    <row r="12" spans="1:14">
       <c r="A12" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B12" s="7">
         <v>19.563</v>
       </c>
-      <c r="C12" s="7">
+      <c r="C12" s="8">
         <v>1</v>
       </c>
       <c r="D12" s="8">
         <v>0.63</v>
       </c>
-      <c r="E12" s="7">
-        <v>12.32</v>
-      </c>
-      <c r="F12" s="7">
+      <c r="E12" s="8">
+        <v>12.325</v>
+      </c>
+      <c r="F12" s="8">
         <v>12.52</v>
       </c>
     </row>
-    <row r="13" spans="1:15">
+    <row r="13" spans="1:14">
       <c r="A13" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B13" s="10">
         <v>147.264</v>
@@ -894,10 +876,10 @@
       </c>
       <c r="D13" s="8"/>
       <c r="E13" s="10">
-        <v>218.84</v>
+        <v>218.845</v>
       </c>
       <c r="F13" s="10">
-        <v>222.87</v>
+        <v>222.871</v>
       </c>
     </row>
   </sheetData>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП СПОРТ-ВАРНА/ОП СПОРТ-ВАРНА.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП СПОРТ-ВАРНА/ОП СПОРТ-ВАРНА.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="24">
   <si>
     <t>Дата</t>
   </si>
@@ -34,9 +34,6 @@
     <t>Литри</t>
   </si>
   <si>
-    <t>Тип количество</t>
-  </si>
-  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -58,64 +55,19 @@
     <t>Billing_Document</t>
   </si>
   <si>
-    <t>1148 Варна пристанище</t>
-  </si>
-  <si>
-    <t>1146 Варна Сливница</t>
-  </si>
-  <si>
-    <t>В6330РА</t>
-  </si>
-  <si>
-    <t>ТубаСпорт1</t>
-  </si>
-  <si>
-    <t>В8983ВР</t>
-  </si>
-  <si>
-    <t>78970155027720717</t>
-  </si>
-  <si>
-    <t>78970155027720733</t>
-  </si>
-  <si>
-    <t>78970155027720725</t>
-  </si>
-  <si>
-    <t>DIESEL EKONOMY</t>
+    <t>Варна Сливница</t>
+  </si>
+  <si>
+    <t>В2244РМ</t>
+  </si>
+  <si>
+    <t>78970155027720709</t>
   </si>
   <si>
     <t>95 EKONOMY UNLEADED</t>
   </si>
   <si>
-    <t>E GAS LPG</t>
-  </si>
-  <si>
-    <t>L15</t>
-  </si>
-  <si>
-    <t>11:51:00</t>
-  </si>
-  <si>
-    <t>14:28:00</t>
-  </si>
-  <si>
-    <t>14:54:00</t>
-  </si>
-  <si>
-    <t>13:59:00</t>
-  </si>
-  <si>
-    <t>3234948009 3234948009</t>
-  </si>
-  <si>
-    <t>3235464501 3235464501</t>
-  </si>
-  <si>
-    <t>3235622053 3235622053</t>
-  </si>
-  <si>
-    <t>3235636388 3235636388</t>
+    <t>12:03</t>
   </si>
   <si>
     <t>Общи литри по продукт / ОП СПОРТ-ВАРНА</t>
@@ -141,9 +93,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="#,##0.000"/>
+    <numFmt numFmtId="164" formatCode="#,##0.00"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="#,##0.00"/>
+    <numFmt numFmtId="166" formatCode="#,##0.00000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -237,10 +189,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -535,7 +487,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N13"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -544,17 +496,16 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="16.7109375" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="7.7109375" customWidth="1"/>
+    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:13">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -594,297 +545,119 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="3">
+        <v>46237</v>
+      </c>
+      <c r="B2" t="s">
         <v>13</v>
       </c>
+      <c r="C2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2">
+        <v>61.929</v>
+      </c>
+      <c r="G2" s="1">
+        <v>1.52</v>
+      </c>
+      <c r="H2">
+        <v>94.13200000000001</v>
+      </c>
+      <c r="I2" s="1">
+        <v>1.55</v>
+      </c>
+      <c r="J2">
+        <v>95.98999999999999</v>
+      </c>
+      <c r="K2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L2">
+        <v>269848</v>
+      </c>
+      <c r="M2">
+        <v>158647</v>
+      </c>
     </row>
-    <row r="2" spans="1:14">
-      <c r="A2" s="3">
-        <v>46220</v>
-      </c>
-      <c r="B2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C2" t="s">
+    <row r="5" spans="1:13">
+      <c r="A5" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F2">
-        <v>52</v>
-      </c>
-      <c r="G2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H2">
-        <v>1.6</v>
-      </c>
-      <c r="I2" s="1">
-        <v>83.2</v>
-      </c>
-      <c r="J2">
-        <v>1.63</v>
-      </c>
-      <c r="K2" s="1">
-        <v>84.76000000000001</v>
-      </c>
-      <c r="L2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M2">
-        <v>171900</v>
-      </c>
-      <c r="N2" t="s">
-        <v>30</v>
+      <c r="B7" s="7">
+        <v>61.929</v>
+      </c>
+      <c r="C7" s="7">
+        <v>1</v>
+      </c>
+      <c r="D7" s="8">
+        <v>1.52</v>
+      </c>
+      <c r="E7" s="7">
+        <v>94.13</v>
+      </c>
+      <c r="F7" s="7">
+        <v>95.98999999999999</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
-      <c r="A3" s="3">
-        <v>46231</v>
-      </c>
-      <c r="B3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E3" t="s">
+    <row r="8" spans="1:13">
+      <c r="A8" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="F3">
-        <v>40</v>
-      </c>
-      <c r="G3" t="s">
-        <v>25</v>
-      </c>
-      <c r="H3">
-        <v>1.53</v>
-      </c>
-      <c r="I3" s="1">
-        <v>61.2</v>
-      </c>
-      <c r="J3">
-        <v>1.56</v>
-      </c>
-      <c r="K3" s="1">
-        <v>62.4</v>
-      </c>
-      <c r="L3" t="s">
-        <v>27</v>
-      </c>
-      <c r="M3">
-        <v>0</v>
-      </c>
-      <c r="N3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
-      <c r="A4" s="3">
-        <v>46234</v>
-      </c>
-      <c r="B4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F4">
-        <v>35.701</v>
-      </c>
-      <c r="G4" t="s">
-        <v>25</v>
-      </c>
-      <c r="H4">
-        <v>1.74</v>
-      </c>
-      <c r="I4" s="1">
-        <v>62.12</v>
-      </c>
-      <c r="J4">
-        <v>1.77</v>
-      </c>
-      <c r="K4" s="1">
-        <v>63.191</v>
-      </c>
-      <c r="L4" t="s">
-        <v>28</v>
-      </c>
-      <c r="M4">
-        <v>172250</v>
-      </c>
-      <c r="N4" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
-      <c r="A5" s="3">
-        <v>46234</v>
-      </c>
-      <c r="B5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E5" t="s">
-        <v>24</v>
-      </c>
-      <c r="F5">
-        <v>19.563</v>
-      </c>
-      <c r="G5" t="s">
-        <v>25</v>
-      </c>
-      <c r="H5">
-        <v>0.63</v>
-      </c>
-      <c r="I5" s="1">
-        <v>12.325</v>
-      </c>
-      <c r="J5">
-        <v>0.64</v>
-      </c>
-      <c r="K5" s="1">
-        <v>12.52</v>
-      </c>
-      <c r="L5" t="s">
-        <v>29</v>
-      </c>
-      <c r="M5">
-        <v>68303</v>
-      </c>
-      <c r="N5" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
-      <c r="A8" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-    </row>
-    <row r="9" spans="1:14">
-      <c r="A9" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
-      <c r="A10" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B10" s="7">
-        <v>87.70099999999999</v>
-      </c>
-      <c r="C10" s="8">
-        <v>2</v>
-      </c>
-      <c r="D10" s="8">
-        <v>1.657</v>
-      </c>
-      <c r="E10" s="8">
-        <v>145.32</v>
-      </c>
-      <c r="F10" s="8">
-        <v>147.951</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
-      <c r="A11" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="B11" s="7">
-        <v>40</v>
-      </c>
-      <c r="C11" s="8">
+      <c r="B8" s="10">
+        <v>61.929</v>
+      </c>
+      <c r="C8" s="10">
         <v>1</v>
       </c>
-      <c r="D11" s="8">
-        <v>1.53</v>
-      </c>
-      <c r="E11" s="8">
-        <v>61.2</v>
-      </c>
-      <c r="F11" s="8">
-        <v>62.4</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14">
-      <c r="A12" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="B12" s="7">
-        <v>19.563</v>
-      </c>
-      <c r="C12" s="8">
-        <v>1</v>
-      </c>
-      <c r="D12" s="8">
-        <v>0.63</v>
-      </c>
-      <c r="E12" s="8">
-        <v>12.325</v>
-      </c>
-      <c r="F12" s="8">
-        <v>12.52</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14">
-      <c r="A13" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="B13" s="10">
-        <v>147.264</v>
-      </c>
-      <c r="C13" s="10">
-        <v>4</v>
-      </c>
-      <c r="D13" s="8"/>
-      <c r="E13" s="10">
-        <v>218.845</v>
-      </c>
-      <c r="F13" s="10">
-        <v>222.871</v>
+      <c r="D8" s="8"/>
+      <c r="E8" s="10">
+        <v>94.13</v>
+      </c>
+      <c r="F8" s="10">
+        <v>95.98999999999999</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="A5:F5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП СПОРТ-ВАРНА/ОП СПОРТ-ВАРНА.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП СПОРТ-ВАРНА/ОП СПОРТ-ВАРНА.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="43">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -55,19 +58,73 @@
     <t>Billing_Document</t>
   </si>
   <si>
-    <t>Варна Сливница</t>
+    <t>1148 Варна пристанище</t>
+  </si>
+  <si>
+    <t>1199 Varna Car Osvoboditel</t>
+  </si>
+  <si>
+    <t>1146 Варна Сливница</t>
+  </si>
+  <si>
+    <t>ТубаСпорт2</t>
+  </si>
+  <si>
+    <t>ТубаСпорт1</t>
+  </si>
+  <si>
+    <t>В6330РА</t>
   </si>
   <si>
     <t>В2244РМ</t>
   </si>
   <si>
+    <t>78970155027722143</t>
+  </si>
+  <si>
+    <t>78970155027720733</t>
+  </si>
+  <si>
+    <t>78970155027720717</t>
+  </si>
+  <si>
     <t>78970155027720709</t>
   </si>
   <si>
+    <t>DIESEL EKONOMY</t>
+  </si>
+  <si>
     <t>95 EKONOMY UNLEADED</t>
   </si>
   <si>
-    <t>12:03</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>13:35:00</t>
+  </si>
+  <si>
+    <t>11:41:00</t>
+  </si>
+  <si>
+    <t>11:38:00</t>
+  </si>
+  <si>
+    <t>09:51:00</t>
+  </si>
+  <si>
+    <t>3236615398 3236615398</t>
+  </si>
+  <si>
+    <t>3236669997 3236669997</t>
+  </si>
+  <si>
+    <t>3236671264 3236671264</t>
+  </si>
+  <si>
+    <t>3236672025 3236672025</t>
+  </si>
+  <si>
+    <t>3236895036 3236895036</t>
   </si>
   <si>
     <t>Общи литри по продукт / ОП СПОРТ-ВАРНА</t>
@@ -92,10 +149,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="#,##0.00"/>
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="#,##0.000"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="#,##0.00000"/>
+    <numFmt numFmtId="166" formatCode="#,##0.00"/>
+    <numFmt numFmtId="167" formatCode="#,##0.00000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -175,7 +233,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -189,10 +247,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -487,7 +547,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:N13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -496,16 +556,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="7.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -545,119 +606,321 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:13">
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" s="3">
-        <v>46237</v>
+        <v>46253</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2">
+        <v>20</v>
+      </c>
+      <c r="G2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H2" s="1">
+        <v>1.677</v>
+      </c>
+      <c r="I2" s="1">
+        <v>33.54</v>
+      </c>
+      <c r="J2" s="1">
+        <v>1.82</v>
+      </c>
+      <c r="K2" s="1">
+        <v>36.4</v>
+      </c>
+      <c r="L2" t="s">
+        <v>28</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" s="3">
+        <v>46254</v>
+      </c>
+      <c r="B3" t="s">
         <v>15</v>
       </c>
-      <c r="E2" t="s">
+      <c r="C3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F3">
+        <v>20</v>
+      </c>
+      <c r="G3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H3" s="1">
+        <v>1.429</v>
+      </c>
+      <c r="I3" s="1">
+        <v>28.58</v>
+      </c>
+      <c r="J3" s="1">
+        <v>1.57</v>
+      </c>
+      <c r="K3" s="1">
+        <v>31.4</v>
+      </c>
+      <c r="L3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" s="3">
+        <v>46254</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4">
+        <v>20</v>
+      </c>
+      <c r="G4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H4" s="1">
+        <v>1.429</v>
+      </c>
+      <c r="I4" s="1">
+        <v>28.58</v>
+      </c>
+      <c r="J4" s="1">
+        <v>1.57</v>
+      </c>
+      <c r="K4" s="1">
+        <v>31.4</v>
+      </c>
+      <c r="L4" t="s">
+        <v>30</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5" s="3">
+        <v>46254</v>
+      </c>
+      <c r="B5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5">
+        <v>35</v>
+      </c>
+      <c r="G5" t="s">
+        <v>27</v>
+      </c>
+      <c r="H5" s="1">
+        <v>1.689</v>
+      </c>
+      <c r="I5" s="1">
+        <v>59.115</v>
+      </c>
+      <c r="J5" s="1">
+        <v>1.84</v>
+      </c>
+      <c r="K5" s="1">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="L5" t="s">
+        <v>30</v>
+      </c>
+      <c r="M5">
+        <v>172520</v>
+      </c>
+      <c r="N5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="A6" s="3">
+        <v>46259</v>
+      </c>
+      <c r="B6" t="s">
         <v>16</v>
       </c>
-      <c r="F2">
-        <v>61.929</v>
-      </c>
-      <c r="G2" s="1">
-        <v>1.52</v>
-      </c>
-      <c r="H2">
-        <v>94.13200000000001</v>
-      </c>
-      <c r="I2" s="1">
-        <v>1.55</v>
-      </c>
-      <c r="J2">
-        <v>95.98999999999999</v>
-      </c>
-      <c r="K2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L2">
-        <v>269848</v>
-      </c>
-      <c r="M2">
-        <v>158647</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B6" s="5" t="s">
+      <c r="C6" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" s="7">
-        <v>61.929</v>
-      </c>
-      <c r="C7" s="7">
-        <v>1</v>
-      </c>
-      <c r="D7" s="8">
-        <v>1.52</v>
-      </c>
-      <c r="E7" s="7">
-        <v>94.13</v>
-      </c>
-      <c r="F7" s="7">
-        <v>95.98999999999999</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="B8" s="10">
-        <v>61.929</v>
-      </c>
-      <c r="C8" s="10">
-        <v>1</v>
-      </c>
-      <c r="D8" s="8"/>
-      <c r="E8" s="10">
-        <v>94.13</v>
-      </c>
-      <c r="F8" s="10">
-        <v>95.98999999999999</v>
+      <c r="D6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F6">
+        <v>56.37</v>
+      </c>
+      <c r="G6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H6" s="1">
+        <v>1.459</v>
+      </c>
+      <c r="I6" s="1">
+        <v>82.244</v>
+      </c>
+      <c r="J6" s="1">
+        <v>1.58</v>
+      </c>
+      <c r="K6" s="1">
+        <v>89.065</v>
+      </c>
+      <c r="L6" t="s">
+        <v>31</v>
+      </c>
+      <c r="M6">
+        <v>270285</v>
+      </c>
+      <c r="N6" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11" s="7">
+        <v>96.37</v>
+      </c>
+      <c r="C11" s="8">
+        <v>3</v>
+      </c>
+      <c r="D11" s="9">
+        <v>1.44655</v>
+      </c>
+      <c r="E11" s="7">
+        <v>139.4</v>
+      </c>
+      <c r="F11" s="7">
+        <v>151.86</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" s="7">
+        <v>55</v>
+      </c>
+      <c r="C12" s="8">
+        <v>2</v>
+      </c>
+      <c r="D12" s="9">
+        <v>1.68464</v>
+      </c>
+      <c r="E12" s="7">
+        <v>92.66</v>
+      </c>
+      <c r="F12" s="7">
+        <v>100.8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="B13" s="11">
+        <v>151.37</v>
+      </c>
+      <c r="C13" s="12">
+        <v>5</v>
+      </c>
+      <c r="D13" s="9"/>
+      <c r="E13" s="11">
+        <v>232.06</v>
+      </c>
+      <c r="F13" s="11">
+        <v>252.66</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A9:F9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП СПОРТ-ВАРНА/ОП СПОРТ-ВАРНА.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП СПОРТ-ВАРНА/ОП СПОРТ-ВАРНА.xlsx
@@ -633,10 +633,10 @@
         <v>27</v>
       </c>
       <c r="H2" s="1">
-        <v>1.677</v>
+        <v>1.79</v>
       </c>
       <c r="I2" s="1">
-        <v>33.54</v>
+        <v>35.8</v>
       </c>
       <c r="J2" s="1">
         <v>1.82</v>
@@ -677,10 +677,10 @@
         <v>27</v>
       </c>
       <c r="H3" s="1">
-        <v>1.429</v>
+        <v>1.54</v>
       </c>
       <c r="I3" s="1">
-        <v>28.58</v>
+        <v>30.8</v>
       </c>
       <c r="J3" s="1">
         <v>1.57</v>
@@ -721,10 +721,10 @@
         <v>27</v>
       </c>
       <c r="H4" s="1">
-        <v>1.429</v>
+        <v>1.54</v>
       </c>
       <c r="I4" s="1">
-        <v>28.58</v>
+        <v>30.8</v>
       </c>
       <c r="J4" s="1">
         <v>1.57</v>
@@ -765,10 +765,10 @@
         <v>27</v>
       </c>
       <c r="H5" s="1">
-        <v>1.689</v>
+        <v>1.81</v>
       </c>
       <c r="I5" s="1">
-        <v>59.115</v>
+        <v>63.35</v>
       </c>
       <c r="J5" s="1">
         <v>1.84</v>
@@ -809,10 +809,10 @@
         <v>27</v>
       </c>
       <c r="H6" s="1">
-        <v>1.459</v>
+        <v>1.55</v>
       </c>
       <c r="I6" s="1">
-        <v>82.244</v>
+        <v>87.374</v>
       </c>
       <c r="J6" s="1">
         <v>1.58</v>
@@ -871,10 +871,10 @@
         <v>3</v>
       </c>
       <c r="D11" s="9">
-        <v>1.44655</v>
+        <v>1.54585</v>
       </c>
       <c r="E11" s="7">
-        <v>139.4</v>
+        <v>148.97</v>
       </c>
       <c r="F11" s="7">
         <v>151.86</v>
@@ -891,10 +891,10 @@
         <v>2</v>
       </c>
       <c r="D12" s="9">
-        <v>1.68464</v>
+        <v>1.80273</v>
       </c>
       <c r="E12" s="7">
-        <v>92.66</v>
+        <v>99.15000000000001</v>
       </c>
       <c r="F12" s="7">
         <v>100.8</v>
@@ -912,7 +912,7 @@
       </c>
       <c r="D13" s="9"/>
       <c r="E13" s="11">
-        <v>232.06</v>
+        <v>248.12</v>
       </c>
       <c r="F13" s="11">
         <v>252.66</v>
